--- a/用卷/xlsx/2003.xlsx
+++ b/用卷/xlsx/2003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC61F958-B5E4-4871-9F1D-A63A8ED61990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43C0D35-09D8-4AA4-994A-AB8E8FB6C907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,10 +259,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>新课程卷,旧课程卷,新课程理综卷,旧课程理综卷,全国春考卷,上海卷,贵州卷,云南卷</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>新课程卷文理,旧课程卷文理,全国春考卷文理,北京春考卷文理,河南卷,辽宁卷,
 上海春考卷,秋考卷文理,江苏卷,广东广西卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -285,6 +281,10 @@
   </si>
   <si>
     <t>语文、英语为全国卷,其他科目为旧课程理综/文综卷</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新课程卷,旧课程卷,新课程理综卷,旧课程理综卷,全国春考卷,上海卷,云南卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1030,7 +1030,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D25" s="14"/>
     </row>
@@ -1042,7 +1042,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="14"/>
     </row>
@@ -1093,7 +1093,7 @@
         <v>64</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1107,7 +1107,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1178,7 +1178,7 @@
         <v>27</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="11"/>
     </row>
@@ -1228,7 +1228,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D42" s="8"/>
     </row>
@@ -1273,10 +1273,10 @@
         <v>37</v>
       </c>
       <c r="B46" s="4">
-        <v>8</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>69</v>
+        <v>7</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="D46" s="8"/>
     </row>
